--- a/S_数据表/Occupation_Template.xlsx
+++ b/S_数据表/Occupation_Template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885A515A-AF52-48C3-A866-578901C5A488}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCE2F56-E189-48AE-AB01-B455E684BBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="57">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -271,6 +271,14 @@
   </si>
   <si>
     <t>BaseDefAdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑暗武士</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1367,9 +1375,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1407,9 +1415,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1442,26 +1450,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1494,26 +1485,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2366,34 +2340,88 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
+    <row r="9" spans="1:27" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="11">
+        <v>450</v>
+      </c>
+      <c r="D9" s="11">
+        <v>50</v>
+      </c>
+      <c r="E9" s="11">
+        <v>100</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
+        <v>30</v>
+      </c>
+      <c r="I9" s="11">
+        <v>40</v>
+      </c>
+      <c r="J9" s="11">
+        <v>30</v>
+      </c>
+      <c r="K9" s="11">
+        <v>40</v>
+      </c>
+      <c r="L9" s="12">
+        <v>4</v>
+      </c>
+      <c r="M9" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="N9" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="O9" s="12">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="R9" s="12">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>75</v>
+      </c>
+      <c r="T9" s="11">
+        <v>4</v>
+      </c>
+      <c r="U9" s="11">
+        <v>8</v>
+      </c>
+      <c r="V9" s="11">
+        <v>0</v>
+      </c>
+      <c r="W9" s="11">
+        <v>0</v>
+      </c>
+      <c r="X9" s="11">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="11">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="11">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="11">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
